--- a/results/table_relevant.xlsx
+++ b/results/table_relevant.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="98">
   <si>
     <t>Authors</t>
   </si>
@@ -46,99 +46,111 @@
     <t>Sheng et al.</t>
   </si>
   <si>
+    <t>Das et al.</t>
+  </si>
+  <si>
     <t>Xie et al.</t>
   </si>
   <si>
-    <t>Das et al.</t>
+    <t>Anand et al.</t>
   </si>
   <si>
     <t>Xiu et al.</t>
   </si>
   <si>
-    <t>Anand et al.</t>
+    <t>Prusty et al.</t>
   </si>
   <si>
     <t>Liang et al.</t>
   </si>
   <si>
-    <t>Prusty et al.</t>
+    <t>Liu et al.</t>
+  </si>
+  <si>
+    <t>Khadidos et al.</t>
+  </si>
+  <si>
+    <t>Chen et al.</t>
+  </si>
+  <si>
+    <t>Jing et al.</t>
+  </si>
+  <si>
+    <t>Pareek et al.</t>
+  </si>
+  <si>
+    <t>Yang et al.</t>
+  </si>
+  <si>
+    <t>Wang et al.</t>
+  </si>
+  <si>
+    <t>Li et al.</t>
   </si>
   <si>
     <t>He et al.</t>
   </si>
   <si>
-    <t>Yang et al.</t>
-  </si>
-  <si>
-    <t>Chen et al.</t>
-  </si>
-  <si>
-    <t>Jing et al.</t>
-  </si>
-  <si>
     <t>Xu et al.</t>
   </si>
   <si>
-    <t>Wang et al.</t>
-  </si>
-  <si>
-    <t>Khadidos et al.</t>
-  </si>
-  <si>
-    <t>Pareek et al.</t>
-  </si>
-  <si>
     <t>Magnetic resonance image markers to improve patient-specific prediction of IMRT-induced rectal toxicity in prostate cancer patients</t>
   </si>
   <si>
     <t>Application of MRI Image Based on Computer Semiautomatic Segmentation Algorithm in the Classification Prediction of Breast Cancer Histology</t>
   </si>
   <si>
+    <t>Brain tumor segmentation and overall survival period prediction in glioblastoma multiforme using radiomic features</t>
+  </si>
+  <si>
     <t>Analysis of the Diagnosis Model of Peripheral Non-Small-Cell Lung Cancer under Computed Tomography Images</t>
   </si>
   <si>
-    <t>Brain tumor segmentation and overall survival period prediction in glioblastoma multiforme using radiomic features</t>
-  </si>
-  <si>
     <t>Diagnostic Efficacy of CT Radiomic Features in Pulmonary Invasive Mucinous Adenocarcinoma</t>
   </si>
   <si>
+    <t>Diagnosis of Prostate Cancer Using GLCM Enabled KNN Technique by Analyzing MRI Images</t>
+  </si>
+  <si>
     <t>Integrative Nomogram of Computed Tomography Radiomics, Clinical, and Tumor Immune Features for Analysis of Disease-Free Survival of NSCLC Patients with Surgery</t>
   </si>
   <si>
-    <t>Diagnosis of Prostate Cancer Using GLCM Enabled KNN Technique by Analyzing MRI Images</t>
+    <t>Prediction of Breast cancer using integrated machine learning-fuzzy and dimension reduction techniques</t>
   </si>
   <si>
     <t>Renal enhanced CT images reveal the tandem mechanism between tumor cells and immunocytes based on bulk/single-cell RNA sequencing</t>
   </si>
   <si>
-    <t>Prediction of Breast cancer using integrated machine learning-fuzzy and dimension reduction techniques</t>
+    <t>Clinical study on forecasting the prognosis of patients with cerebellar hemorrhage based on CT radiomics models</t>
+  </si>
+  <si>
+    <t>Evaluation of the Risk of Recurrence in Patients with Local Advanced Rectal Tumours by Different Radiomic Analysis Approaches (Retracted Article)</t>
+  </si>
+  <si>
+    <t>A hybrid feature selection-based brain tumor detection and segmentation in multiparametric magnetic resonance imaging (Withdrawn Publication. See vol. 49, pg. 2875, 2022)</t>
+  </si>
+  <si>
+    <t>Multimodal MRI-Based Radiomic Nomogram for the Early Differentiation of Recurrence and Pseudoprogression of High-Grade Glioma (Retracted Article)</t>
+  </si>
+  <si>
+    <t>Predicting the Spread of Vessels in Initial Stage Cervical Cancer through Radiomics Strategy Based on Deep Learning Approach (Retracted Article)</t>
+  </si>
+  <si>
+    <t>Prediction of Changes in Tumor Regression during Radiotherapy for Nasopharyngeal Carcinoma by Using the Computed Tomography-Based Radiomics (Retracted Article)</t>
+  </si>
+  <si>
+    <t>Feasibility of Constructing an Automatic Meniscus Injury Detection Model Based on Dual-Mode Magnetic Resonance Imaging (MRI) Radiomics of the Knee Joint (Retracted Article)</t>
+  </si>
+  <si>
+    <t>Preoperative prediction of lymph node metastasis in colorectal cancer based on intratumoral and peritumoral CT radiomics nomogram</t>
   </si>
   <si>
     <t>Recurrence of Early Hepatocellular Carcinoma after Surgery May Be Related to Intestinal Oxidative Stress and the Development of a Predictive Model (Retracted Article)</t>
   </si>
   <si>
-    <t>Prediction of Changes in Tumor Regression during Radiotherapy for Nasopharyngeal Carcinoma by Using the Computed Tomography-Based Radiomics (Retracted Article)</t>
-  </si>
-  <si>
-    <t>A hybrid feature selection-based brain tumor detection and segmentation in multiparametric magnetic resonance imaging (Withdrawn Publication. See vol. 49, pg. 2875, 2022)</t>
-  </si>
-  <si>
-    <t>Multimodal MRI-Based Radiomic Nomogram for the Early Differentiation of Recurrence and Pseudoprogression of High-Grade Glioma (Retracted Article)</t>
-  </si>
-  <si>
     <t>Severity Assessment of COVID-19 Using a CT-Based Radiomics Model (Retracted Article)</t>
   </si>
   <si>
-    <t>Feasibility of Constructing an Automatic Meniscus Injury Detection Model Based on Dual-Mode Magnetic Resonance Imaging (MRI) Radiomics of the Knee Joint (Retracted Article)</t>
-  </si>
-  <si>
-    <t>Evaluation of the Risk of Recurrence in Patients with Local Advanced Rectal Tumours by Different Radiomic Analysis Approaches (Retracted Article)</t>
-  </si>
-  <si>
-    <t>Predicting the Spread of Vessels in Initial Stage Cervical Cancer through Radiomics Strategy Based on Deep Learning Approach (Retracted Article)</t>
-  </si>
-  <si>
     <t>Value of CT Radiomics and Clinical Features in Predicting Bone Metastases in Patients with NSCLC (Retracted Article)</t>
   </si>
   <si>
@@ -154,43 +166,52 @@
     <t>Scanning</t>
   </si>
   <si>
+    <t>BioMed Research International</t>
+  </si>
+  <si>
     <t>Journal of Oncology</t>
   </si>
   <si>
-    <t>BioMed Research International</t>
+    <t>Journal of Intelligent and Fuzzy Systems</t>
   </si>
   <si>
     <t>Functional and Integrative Genomics</t>
   </si>
   <si>
-    <t>Journal of Intelligent and Fuzzy Systems</t>
+    <t>Neuroscience Informatics</t>
+  </si>
+  <si>
+    <t>Applied Bionics and Biomechanics</t>
+  </si>
+  <si>
+    <t>Advances in Materials Science and Engineering</t>
+  </si>
+  <si>
+    <t>Contrast Media &amp; Molecular Imaging</t>
+  </si>
+  <si>
+    <t>Computational and Mathematical Methods in Medicine</t>
+  </si>
+  <si>
+    <t>Cancer Treatment and Research Communications</t>
   </si>
   <si>
     <t>Oxidative Medicine and Cellular Longevity</t>
   </si>
   <si>
-    <t>Contrast Media &amp; Molecular Imaging</t>
-  </si>
-  <si>
     <t>Stem Cells International</t>
   </si>
   <si>
-    <t>Computational and Mathematical Methods in Medicine</t>
-  </si>
-  <si>
-    <t>Applied Bionics and Biomechanics</t>
-  </si>
-  <si>
-    <t>Advances in Materials Science and Engineering</t>
-  </si>
-  <si>
     <t>WILEY</t>
   </si>
   <si>
+    <t>Sage</t>
+  </si>
+  <si>
     <t>Springer</t>
   </si>
   <si>
-    <t>Sage</t>
+    <t>Elsevier BV</t>
   </si>
   <si>
     <t>Iran</t>
@@ -211,51 +232,57 @@
     <t>10.1155/2021/6088322</t>
   </si>
   <si>
+    <t>10.1002/cpe.6501</t>
+  </si>
+  <si>
     <t>10.1155/2022/3107965</t>
   </si>
   <si>
-    <t>10.1002/cpe.6501</t>
-  </si>
-  <si>
     <t>10.1155/2022/5314225</t>
   </si>
   <si>
+    <t>10.1155/2023/3913351</t>
+  </si>
+  <si>
     <t>10.1155/2023/8607062</t>
   </si>
   <si>
-    <t>10.1155/2023/3913351</t>
+    <t>10.3233/JIFS-223265</t>
   </si>
   <si>
     <t>10.1007/s10142-023-01011-5</t>
   </si>
   <si>
-    <t>10.3233/JIFS-223265</t>
+    <t>10.1016/j.neuri.2024.100163</t>
+  </si>
+  <si>
+    <t>10.1155/2021/4520450</t>
+  </si>
+  <si>
+    <t>10.1002/mp.15035</t>
+  </si>
+  <si>
+    <t>10.1155/2022/4667117</t>
+  </si>
+  <si>
+    <t>10.1155/2022/1008652</t>
+  </si>
+  <si>
+    <t>10.1155/2022/3417480</t>
+  </si>
+  <si>
+    <t>10.1155/2022/2155132</t>
+  </si>
+  <si>
+    <t>10.3390/cancers14030661</t>
   </si>
   <si>
     <t>10.1155/2022/7261786</t>
   </si>
   <si>
-    <t>10.1155/2022/3417480</t>
-  </si>
-  <si>
-    <t>10.1002/mp.15035</t>
-  </si>
-  <si>
-    <t>10.1155/2022/4667117</t>
-  </si>
-  <si>
     <t>10.1155/2021/2263469</t>
   </si>
   <si>
-    <t>10.1155/2022/2155132</t>
-  </si>
-  <si>
-    <t>10.1155/2021/4520450</t>
-  </si>
-  <si>
-    <t>10.1155/2022/1008652</t>
-  </si>
-  <si>
     <t>10.1155/2022/7642511</t>
   </si>
   <si>
@@ -271,10 +298,13 @@
     <t>Systematic manipulation</t>
   </si>
   <si>
+    <t>Inadequate peer review</t>
+  </si>
+  <si>
     <t>Compromised editorial/peer review</t>
   </si>
   <si>
-    <t>Inadequate peer review</t>
+    <t>Author retraction</t>
   </si>
   <si>
     <t>Duplicate article</t>
@@ -635,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -666,28 +696,28 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I2">
         <v>2019</v>
@@ -701,22 +731,22 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I3">
         <v>2021</v>
@@ -724,28 +754,28 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I4">
         <v>2022</v>
@@ -753,28 +783,28 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I5">
         <v>2022</v>
@@ -782,28 +812,28 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I6">
         <v>2022</v>
@@ -811,28 +841,28 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G7" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I7">
         <v>2023</v>
@@ -840,28 +870,28 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I8">
         <v>2023</v>
@@ -869,28 +899,28 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="I9">
         <v>2023</v>
@@ -898,28 +928,28 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="I10">
         <v>2023</v>
@@ -927,57 +957,57 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="I11">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I12">
         <v>2025</v>
@@ -991,22 +1021,22 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="I13">
         <v>2025</v>
@@ -1014,28 +1044,28 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I14">
         <v>2025</v>
@@ -1043,28 +1073,28 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I15">
         <v>2025</v>
@@ -1072,28 +1102,28 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G16" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H16" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I16">
         <v>2025</v>
@@ -1101,28 +1131,28 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H17" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I17">
         <v>2025</v>
@@ -1130,28 +1160,28 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G18" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I18">
         <v>2025</v>
@@ -1159,30 +1189,88 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="1">
+        <v>75</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1">
+        <v>82</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" t="s">
         <v>89</v>
       </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" t="s">
-        <v>82</v>
-      </c>
-      <c r="I19">
+      <c r="H21" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21">
         <v>2025</v>
       </c>
     </row>
